--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:13</t>
+    <t xml:space="preserve">2026-09-09 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:07</t>
+    <t xml:space="preserve">2026-09-17 14:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:04</t>
+    <t xml:space="preserve">2026-09-23 12:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:33</t>
+    <t xml:space="preserve">2026-10-02 13:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:27</t>
+    <t xml:space="preserve">2026-10-05 10:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -571,7 +571,7 @@
         <v>2018</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>393629.12</v>
+        <v>393629.13</v>
       </c>
     </row>
     <row r="3">
